--- a/data/EVALUACIONES/PESO/PESO.xlsx
+++ b/data/EVALUACIONES/PESO/PESO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\PESO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF17ADD-A912-44C9-A44E-852D4A375608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F65EBB-E3AC-47E3-89DA-673FB22AC8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,6 +511,9 @@
       <c r="B5" t="s">
         <v>25</v>
       </c>
+      <c r="C5">
+        <v>78.8</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
